--- a/artfynd/A 61488-2022 artfynd.xlsx
+++ b/artfynd/A 61488-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129534904</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2022 artfynd.xlsx
+++ b/artfynd/A 61488-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129534904</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2022 artfynd.xlsx
+++ b/artfynd/A 61488-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129534904</v>
       </c>
       <c r="B2" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2022 artfynd.xlsx
+++ b/artfynd/A 61488-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129534904</v>
       </c>
       <c r="B2" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
